--- a/data/trans_orig/IP2901-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>26709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60911</t>
+          <t>60649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73759</t>
+          <t>74055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>64262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115773</t>
+          <t>117158</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>135137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>57186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81387</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79779</t>
+          <t>80761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107116</t>
+          <t>107520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143085</t>
+          <t>143090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>179783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>33197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40335</t>
+          <t>39963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>43583</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67133</t>
+          <t>67167</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>302514</t>
+          <t>301922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>328261</t>
+          <t>328565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>328627</t>
+          <t>327318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359179</t>
+          <t>359484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>638311</t>
+          <t>640238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>679878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24472</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45393</t>
+          <t>46215</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67739</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118609</t>
+          <t>117853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136913</t>
+          <t>135734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113866</t>
+          <t>114190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130287</t>
+          <t>130577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237237</t>
+          <t>235503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261516</t>
+          <t>261611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>105748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>135276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117646</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151979</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231372</t>
+          <t>232097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279068</t>
+          <t>280283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,82 +2228,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38201</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>86821</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>73989</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>102515</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>48675</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>38691</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>59223</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>86821</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>73336</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>101882</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>492897</t>
+          <t>494202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>528087</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>507142</t>
+          <t>504873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544366</t>
+          <t>544081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1010825</t>
+          <t>1008520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1061133</t>
+          <t>1062523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54929</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51114</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66718</t>
+          <t>65772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62392</t>
+          <t>61889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103282</t>
+          <t>103936</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124325</t>
+          <t>123792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88238</t>
+          <t>88424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117220</t>
+          <t>117377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112383</t>
+          <t>112357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144643</t>
+          <t>145529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209996</t>
+          <t>210242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253075</t>
+          <t>253506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>42076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75270</t>
+          <t>75416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299732</t>
+          <t>299367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>331866</t>
+          <t>330307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>312522</t>
+          <t>313339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>347951</t>
+          <t>347681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>623458</t>
+          <t>622541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668235</t>
+          <t>669656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47008</t>
+          <t>46135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53660</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>76691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51087</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112392</t>
+          <t>113831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131842</t>
+          <t>131810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95315</t>
+          <t>95799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115816</t>
+          <t>116955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214936</t>
+          <t>214957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>242330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169164</t>
+          <t>170311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168130</t>
+          <t>167165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209274</t>
+          <t>206608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312236</t>
+          <t>312485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>365278</t>
+          <t>367419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72671</t>
+          <t>74211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100966</t>
+          <t>102348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136664</t>
+          <t>136575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>479691</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>518918</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>470008</t>
+          <t>473780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>514985</t>
+          <t>516965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>960653</t>
+          <t>958069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1019710</t>
+          <t>1018754</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>25947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42248</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>51371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46675</t>
+          <t>46747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>57547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92298</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106479</t>
+          <t>107109</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>71795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>99578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80373</t>
+          <t>80789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134586</t>
+          <t>132924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170046</t>
+          <t>169114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68016</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95890</t>
+          <t>94730</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322481</t>
+          <t>323780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>353316</t>
+          <t>353775</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>346220</t>
+          <t>347148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>376913</t>
+          <t>377844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679246</t>
+          <t>680656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722585</t>
+          <t>721775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46567</t>
+          <t>46975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124783</t>
+          <t>125810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142618</t>
+          <t>142420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140941</t>
+          <t>141668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>157997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>271766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298358</t>
+          <t>297357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125865</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>112009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>185984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228850</t>
+          <t>226982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103674</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139203</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>503032</t>
+          <t>500158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>537980</t>
+          <t>537504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>584236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1061791</t>
+          <t>1062684</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1112951</t>
+          <t>1111404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2901-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17303</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11873</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24339</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13663</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14031</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25936</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17303</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12136</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23674</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>45737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9341</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14124</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2587</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9341</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5391</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14803</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>58177</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51011</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>65065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>76,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>67970</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60649</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74055</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>60987</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>73416</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>75,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>67,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>82,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>58177</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51064</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64262</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>68,59%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117158</t>
+          <t>116911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>135137</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84821</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84821</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84821</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90122</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90122</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90122</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>84821</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>84821</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93660</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80608</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107840</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68143</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57186</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82530</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57070</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>80352</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>16,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93660</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80761</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107520</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143090</t>
+          <t>142760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179783</t>
+          <t>180419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30560</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22512</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40399</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>24555</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33197</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17748</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>32663</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,01%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30560</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22830</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>39963</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43583</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>343865</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>329122</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>360007</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>315618</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>301922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>328565</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>303251</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>329790</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>77,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>343865</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>327318</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>359484</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640238</t>
+          <t>639364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>679878</t>
+          <t>678845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>468085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>468085</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>468085</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>408315</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>408315</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>408315</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>468085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>468085</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>468085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23796</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17549</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32512</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32234</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>25217</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41400</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24933</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42164</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>18,9%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17192</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>44504</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70365</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8774</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14411</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11005</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6679</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17362</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6337</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17106</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8774</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4623</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13776</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122944</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114160</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>127306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>117853</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>135734</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>116936</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>135392</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>122944</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>114190</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130577</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235503</t>
+          <t>237752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261611</t>
+          <t>262997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>155514</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155514</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>155514</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170544</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170544</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170544</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>155514</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>155514</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>155514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134759</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119243</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>153483</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>119941</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>105748</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>135276</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>105736</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>137502</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>134759</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>118556</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>153294</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232097</t>
+          <t>231811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280283</t>
+          <t>277821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38180</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59962</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>38146</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29718</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>49112</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>29670</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>47914</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>48675</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>38201</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>60140</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>72700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102515</t>
+          <t>101846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>524986</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>506904</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>543084</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>71,55%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>762</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>510893</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>494202</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>527609</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>493259</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>527277</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>76,37%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>524986</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>504873</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>544081</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>74,11%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1008520</t>
+          <t>1009709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1062523</t>
+          <t>1058849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>708420</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>708420</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>708420</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>668980</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>708420</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>708420</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>708420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21875</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15883</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29110</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22170</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29895</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16145</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29265</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21875</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15528</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29162</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>53480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2890,72 +2890,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6132</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3089</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11320</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10063</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6117</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16504</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16073</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>11,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6132</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10909</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -3003,72 +3003,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55644</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48232</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62551</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>57,66%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>74,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58769</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>50545</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65772</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>51089</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>65881</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>64,58%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>55644</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>47786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>61889</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>66,52%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103936</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123792</t>
+          <t>124471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83651</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91001</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>127903</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>111568</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142693</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102364</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88424</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>117377</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89028</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>118462</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>127903</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>112357</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>145529</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210242</t>
+          <t>210281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253506</t>
+          <t>253110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30120</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40056</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31985</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24121</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42076</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23301</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>41384</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>7,11%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30120</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22733</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41164</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50497</t>
+          <t>49957</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75416</t>
+          <t>75848</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>331599</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>316700</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>349217</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>315822</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>299367</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>330307</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>299493</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>331689</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>331599</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>313339</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>347681</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>622541</t>
+          <t>619468</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>669656</t>
+          <t>669231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>489622</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>489622</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>489622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>652</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>450171</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>450171</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>450171</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>489622</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>489622</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>489622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37400</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29307</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47003</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22,28%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27274</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19916</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36389</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19889</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>35999</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,41%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37400</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28071</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>46135</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53717</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76691</t>
+          <t>77566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -3802,72 +3802,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24182</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17338</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32225</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15495</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10426</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22575</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9994</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22079</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24182</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32192</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>49600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106276</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95440</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116735</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>123435</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>113831</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>131810</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>114073</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>132999</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106276</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95799</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>116955</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214957</t>
+          <t>214734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242330</t>
+          <t>243766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167858</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166204</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166204</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166204</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>187178</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>167356</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>207148</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>151808</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>134541</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>170311</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>134546</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>169791</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>187178</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>167165</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>206608</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312485</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367419</t>
+          <t>365619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60435</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>49015</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74469</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>57543</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46414</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>69469</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70340</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>60435</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>47857</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74211</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102348</t>
+          <t>100939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136575</t>
+          <t>138295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>493519</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>470974</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>513575</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>66,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>63,55%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>498026</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>479691</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>518918</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>479121</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>517833</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>70,4%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>493519</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>473780</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>516965</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>958069</t>
+          <t>964689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1018754</t>
+          <t>1021231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>741131</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>741131</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>741131</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>707376</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>741131</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>741131</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>741131</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12063</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7319</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17985</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7024</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12717</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12063</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7762</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18433</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -4945,72 +4945,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3852</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7947</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5829</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46569</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>57505</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>78,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>85,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47191</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42048</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>41590</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>51246</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>81,27%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>52893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>46747</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>57547</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>78,84%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>92376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107109</t>
+          <t>107030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58067</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58067</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58067</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65734</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54115</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78191</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85449</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71795</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99578</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72834</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100176</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>18,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65734</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>55559</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>80789</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132924</t>
+          <t>134696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169114</t>
+          <t>172301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44257</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35247</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>57876</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>35999</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27517</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>47011</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>26939</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>45686</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>7,83%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44257</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34272</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>56280</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66965</t>
+          <t>67266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>96062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>363679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>346687</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>377570</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>513</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>338535</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>323780</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>353775</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>322584</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>353219</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>363679</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>347148</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>377844</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>76,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>680656</t>
+          <t>680145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721775</t>
+          <t>723336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>473670</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>473670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>473670</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>695</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>459984</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>459984</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>459984</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>473670</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>473670</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>473670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5744,72 +5744,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18899</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13013</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25970</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17509</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11878</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24968</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12045</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24888</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18899</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26072</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>46402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15296</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9574</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22570</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18032</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12253</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25084</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11970</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25425</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15296</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22074</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44306</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141097</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>158357</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>134536</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>125810</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>142420</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>124570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>141970</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,1%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>150610</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141668</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>157997</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271766</t>
+          <t>270593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297357</t>
+          <t>297404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184805</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184805</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184805</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170077</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170077</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170077</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184805</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184805</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>96697</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>82070</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>113850</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>109982</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>125738</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>94561</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>125295</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>96697</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>83262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>112009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185984</t>
+          <t>185165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226982</t>
+          <t>229681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -6318,67 +6318,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>61689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>49539</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74131</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>57883</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46880</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>70808</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46867</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70660</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61689</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>50527</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>76109</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>104580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137127</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>567182</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>548657</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>584675</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>520263</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>500158</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>537504</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>501991</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>539107</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>75,61%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>567182</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>548146</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>584236</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1062684</t>
+          <t>1059297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1111404</t>
+          <t>1109957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>688128</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
